--- a/assets/microsoft-office/excel-template/CBC.xlsx
+++ b/assets/microsoft-office/excel-template/CBC.xlsx
@@ -6,12 +6,14 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId5"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="51">
   <si>
     <t xml:space="preserve">               ST. EZEKIEL MORENO CLINICAL LABORATORY</t>
   </si>
@@ -130,16 +132,93 @@
     <t>REMARKS:</t>
   </si>
   <si>
+    <t>ANN DENISE N. JACOBO, RMT</t>
+  </si>
+  <si>
     <t>LENI G. MONTES, MD, FPSP</t>
   </si>
   <si>
+    <t>License No. 79657</t>
+  </si>
+  <si>
     <t>License No. 77395</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="1"/>
+        <sz val="9"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> Medical Technologist</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve"> Pathologist</t>
   </si>
   <si>
     <t xml:space="preserve">            </t>
+  </si>
+  <si>
+    <t>SHAIRA L. MALLARI, RMT</t>
+  </si>
+  <si>
+    <t>License #0077168</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="1"/>
+        <sz val="9"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>KRISHIEL ANN D. VILLALON, RMT, MLS(ASCP</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="1"/>
+        <vertAlign val="superscript"/>
+        <sz val="9"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>i</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="1"/>
+        <sz val="9"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="1"/>
+        <vertAlign val="superscript"/>
+        <sz val="9"/>
+        <color indexed="8"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>CM</t>
+    </r>
+  </si>
+  <si>
+    <t>License #0079651</t>
+  </si>
+  <si>
+    <t>DR. DIANA ROSE LAPUT, M.O III</t>
   </si>
 </sst>
 </file>
@@ -154,7 +233,7 @@
     <font>
       <sz val="11"/>
       <color indexed="8"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="12"/>
@@ -164,7 +243,7 @@
     <font>
       <sz val="14"/>
       <color indexed="8"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="9"/>
@@ -209,11 +288,6 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <b val="1"/>
       <sz val="8"/>
       <color indexed="8"/>
@@ -251,7 +325,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <color indexed="9"/>
+      <color indexed="10"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -272,6 +346,13 @@
       <color indexed="8"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b val="1"/>
+      <vertAlign val="superscript"/>
+      <sz val="9"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -282,7 +363,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="9"/>
+        <fgColor indexed="10"/>
         <bgColor auto="1"/>
       </patternFill>
     </fill>
@@ -297,28 +378,28 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="10"/>
+        <color indexed="9"/>
       </left>
       <right style="thin">
-        <color indexed="10"/>
+        <color indexed="9"/>
       </right>
       <top style="thin">
-        <color indexed="10"/>
+        <color indexed="9"/>
       </top>
       <bottom style="thin">
-        <color indexed="10"/>
+        <color indexed="9"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="10"/>
+        <color indexed="9"/>
       </left>
       <right style="thin">
-        <color indexed="10"/>
+        <color indexed="9"/>
       </right>
       <top style="thin">
-        <color indexed="10"/>
+        <color indexed="9"/>
       </top>
       <bottom style="medium">
         <color indexed="8"/>
@@ -327,10 +408,10 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="10"/>
+        <color indexed="9"/>
       </left>
       <right style="thin">
-        <color indexed="10"/>
+        <color indexed="9"/>
       </right>
       <top style="medium">
         <color indexed="8"/>
@@ -342,16 +423,16 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="10"/>
+        <color indexed="9"/>
       </left>
       <right style="thin">
-        <color indexed="10"/>
+        <color indexed="9"/>
       </right>
       <top style="medium">
         <color indexed="8"/>
       </top>
       <bottom style="thin">
-        <color indexed="10"/>
+        <color indexed="9"/>
       </bottom>
       <diagonal/>
     </border>
@@ -361,26 +442,26 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="3" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="4" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="5" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -392,137 +473,149 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="8" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="9" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="8" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="8" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="14" fontId="8" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="2" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="10" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="8" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="8" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="10" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="18" fontId="8" fillId="2" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="18" fontId="8" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="3" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="11" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="8" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="12" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="2" fontId="8" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="59" fontId="8" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="59" fontId="8" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="2" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="2" fontId="8" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="13" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="8" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="8" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="12" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="3" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="14" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="3" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="12" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="15" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="13" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="15" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="9" fontId="17" fillId="2" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="9" fontId="16" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="3" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="17" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="18" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf numFmtId="9" fontId="16" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="9" fontId="15" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="8" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="19" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="8" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -541,8 +634,8 @@
       <rgbColor rgb="ffff00ff"/>
       <rgbColor rgb="ff00ffff"/>
       <rgbColor rgb="ff000000"/>
+      <rgbColor rgb="ffaaaaaa"/>
       <rgbColor rgb="ffffffff"/>
-      <rgbColor rgb="ffaaaaaa"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -555,13 +648,13 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>609600</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>5079</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>269875</xdr:colOff>
+      <xdr:colOff>384175</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>128903</xdr:rowOff>
+      <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -580,7 +673,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="609600" y="5079"/>
+          <a:off x="609600" y="0"/>
           <a:ext cx="752475" cy="619125"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -599,9 +692,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
-    <a:clrScheme name="Office Theme">
+    <a:clrScheme name="Sheets">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
@@ -615,22 +708,22 @@
         <a:srgbClr val="535353"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
         <a:srgbClr val="0000FF"/>
@@ -639,7 +732,7 @@
         <a:srgbClr val="FF00FF"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office Theme">
+    <a:fontScheme name="Sheets">
       <a:majorFont>
         <a:latin typeface="Helvetica Neue"/>
         <a:ea typeface="Helvetica Neue"/>
@@ -651,7 +744,7 @@
         <a:cs typeface="Helvetica Neue"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office Theme">
+    <a:fmtScheme name="Sheets">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -791,17 +884,17 @@
         <a:solidFill>
           <a:srgbClr val="FFFFFF"/>
         </a:solidFill>
-        <a:ln w="25400" cap="flat">
+        <a:ln w="12700" cap="flat">
           <a:solidFill>
             <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:round/>
+          <a:miter lim="800000"/>
         </a:ln>
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -829,10 +922,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-            <a:sym typeface="Helvetica Neue"/>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -1080,12 +1173,12 @@
     <a:lnDef>
       <a:spPr>
         <a:noFill/>
-        <a:ln w="25400" cap="flat">
+        <a:ln w="12700" cap="flat">
           <a:solidFill>
             <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:round/>
+          <a:miter lim="800000"/>
         </a:ln>
         <a:effectLst/>
         <a:sp3d/>
@@ -1372,7 +1465,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1400,10 +1493,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-            <a:sym typeface="Helvetica Neue"/>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -1655,20 +1748,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultColWidth="14" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="14.3516" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5" style="1" customWidth="1"/>
-    <col min="4" max="4" width="2.17188" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="2.17188" style="1" customWidth="1"/>
-    <col min="7" max="7" width="6.67188" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.35156" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.5" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.85156" style="1" customWidth="1"/>
-    <col min="11" max="26" width="8.5" style="1" customWidth="1"/>
-    <col min="27" max="256" width="14" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12.8516" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.8516" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.35156" style="1" customWidth="1"/>
+    <col min="4" max="4" width="2" style="1" customWidth="1"/>
+    <col min="5" max="5" width="7.67188" style="1" customWidth="1"/>
+    <col min="6" max="6" width="2" style="1" customWidth="1"/>
+    <col min="7" max="7" width="6" style="1" customWidth="1"/>
+    <col min="8" max="8" width="7.5" style="1" customWidth="1"/>
+    <col min="9" max="9" width="7.67188" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8" style="1" customWidth="1"/>
+    <col min="11" max="26" width="7.67188" style="1" customWidth="1"/>
+    <col min="27" max="256" width="12.6719" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="12" customHeight="1">
@@ -1801,7 +1894,7 @@
       </c>
       <c r="F5" s="14">
         <f>TODAY()</f>
-        <v>43953</v>
+        <v>43965</v>
       </c>
       <c r="G5" s="15"/>
       <c r="H5" s="15"/>
@@ -2605,14 +2698,16 @@
       <c r="Z30" s="2"/>
     </row>
     <row r="31" ht="12" customHeight="1">
-      <c r="A31" s="51"/>
+      <c r="A31" t="s" s="51">
+        <v>39</v>
+      </c>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
       <c r="E31" s="2"/>
       <c r="F31" s="52"/>
       <c r="G31" t="s" s="51">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H31" s="6"/>
       <c r="I31" s="6"/>
@@ -2635,14 +2730,16 @@
       <c r="Z31" s="2"/>
     </row>
     <row r="32" ht="12" customHeight="1">
-      <c r="A32" s="51"/>
+      <c r="A32" t="s" s="51">
+        <v>41</v>
+      </c>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
       <c r="E32" s="2"/>
       <c r="F32" s="52"/>
       <c r="G32" t="s" s="51">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H32" s="6"/>
       <c r="I32" s="6"/>
@@ -2693,14 +2790,16 @@
       <c r="Z33" s="2"/>
     </row>
     <row r="34" ht="12" customHeight="1">
-      <c r="A34" s="53"/>
+      <c r="A34" t="s" s="53">
+        <v>43</v>
+      </c>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
       <c r="D34" s="6"/>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
       <c r="G34" t="s" s="25">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H34" s="6"/>
       <c r="I34" s="6"/>
@@ -2761,7 +2860,7 @@
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
       <c r="J36" t="s" s="30">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
@@ -29773,40 +29872,319 @@
       <c r="Z1000" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="27">
+  <mergeCells count="30">
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G31:I31"/>
     <mergeCell ref="G32:I32"/>
     <mergeCell ref="G34:I34"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="G18:I18"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="F5:H5"/>
     <mergeCell ref="F6:H6"/>
     <mergeCell ref="F7:H7"/>
     <mergeCell ref="C11:D11"/>
-    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C22:D22"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="1.01" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr defaultColWidth="12.6667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="5" width="7.67188" style="54" customWidth="1"/>
+    <col min="6" max="256" width="12.6719" style="54" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="16" customHeight="1">
+      <c r="A1" s="55"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+    </row>
+    <row r="2" ht="14.6" customHeight="1">
+      <c r="A2" s="50"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+    </row>
+    <row r="3" ht="14.6" customHeight="1">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+    </row>
+    <row r="4" ht="14.6" customHeight="1">
+      <c r="A4" t="s" s="25">
+        <v>46</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" t="s" s="51">
+        <v>47</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+    </row>
+    <row r="6" ht="14.6" customHeight="1">
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+    </row>
+    <row r="7" ht="14.6" customHeight="1">
+      <c r="A7" t="s" s="25">
+        <v>48</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" t="s" s="51">
+        <v>49</v>
+      </c>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+    </row>
+    <row r="9" ht="14.6" customHeight="1">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+    </row>
+    <row r="10" ht="14.6" customHeight="1">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+    </row>
+    <row r="11" ht="14.6" customHeight="1">
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+    </row>
+    <row r="12" ht="14.6" customHeight="1">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+    </row>
+    <row r="13" ht="14.6" customHeight="1">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+    </row>
+    <row r="14" ht="14.6" customHeight="1">
+      <c r="A14" t="s" s="25">
+        <v>46</v>
+      </c>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" t="s" s="51">
+        <v>47</v>
+      </c>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+    </row>
+    <row r="16" ht="14.6" customHeight="1">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+    </row>
+    <row r="17" ht="14.6" customHeight="1">
+      <c r="A17" t="s" s="25">
+        <v>48</v>
+      </c>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" t="s" s="51">
+        <v>49</v>
+      </c>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+    </row>
+    <row r="19" ht="14.6" customHeight="1">
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+    </row>
+    <row r="20" ht="16.5" customHeight="1">
+      <c r="A20" t="s" s="56">
+        <v>50</v>
+      </c>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A14:D14"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="landscape" pageOrder="downThenOver"/>
+  <headerFooter>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultColWidth="12.6667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="5" width="7.67188" style="57" customWidth="1"/>
+    <col min="6" max="256" width="12.6719" style="57" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="14.6" customHeight="1">
+      <c r="A1" s="6"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+    </row>
+    <row r="2" ht="14.6" customHeight="1">
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+    </row>
+    <row r="3" ht="14.6" customHeight="1">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+    </row>
+    <row r="4" ht="14.6" customHeight="1">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+    </row>
+    <row r="5" ht="14.6" customHeight="1">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+    </row>
+    <row r="6" ht="14.6" customHeight="1">
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+    </row>
+    <row r="7" ht="14.6" customHeight="1">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+    </row>
+    <row r="8" ht="14.6" customHeight="1">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+    </row>
+    <row r="9" ht="14.6" customHeight="1">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+    </row>
+    <row r="10" ht="14.6" customHeight="1">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="landscape" pageOrder="downThenOver"/>
+  <headerFooter>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>